--- a/R_analysis/output/tables/Tabela1_Brasil_anual.xlsx
+++ b/R_analysis/output/tables/Tabela1_Brasil_anual.xlsx
@@ -367,22 +367,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Gestacional_n_casos</t>
+          <t>Gestational_n_casos</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Congênita_n_casos</t>
+          <t>Congenital_n_casos</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Gestacional_taxa_1000nv</t>
+          <t>Gestational_taxa_1000nv</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Congênita_taxa_1000nv</t>
+          <t>Congenital_taxa_1000nv</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
